--- a/backend/exam_data.xlsx
+++ b/backend/exam_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ejcpu\OneDrive\Documents\RDE_EXAM\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047DE18E-C9BA-46A3-9CAE-F97498895A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D59D076-CF06-45F3-8410-F97EBBF2F2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{9DB0D4E1-C020-4474-9086-08C7826413CE}"/>
+    <workbookView xWindow="-20610" yWindow="1590" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{9DB0D4E1-C020-4474-9086-08C7826413CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
   <si>
     <t>QuestionNo</t>
   </si>
@@ -72,12 +72,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>STMicroelectronics.jpg</t>
-  </si>
-  <si>
-    <t>SY100.jpg</t>
-  </si>
-  <si>
     <t>Device-Single-Top-Fullview</t>
   </si>
   <si>
@@ -90,7 +84,94 @@
     <t>Label-Single-Top-Fullview</t>
   </si>
   <si>
-    <t>Texas.jpg</t>
+    <t>blade.jpg</t>
+  </si>
+  <si>
+    <t>blade3.jpg</t>
+  </si>
+  <si>
+    <t>caliper.jpg</t>
+  </si>
+  <si>
+    <t>carrier.jpg</t>
+  </si>
+  <si>
+    <t>cotton.jpg</t>
+  </si>
+  <si>
+    <t>device7.jpg</t>
+  </si>
+  <si>
+    <t>label.jpg</t>
+  </si>
+  <si>
+    <t>others.jpg</t>
+  </si>
+  <si>
+    <t>reel2.jpg</t>
+  </si>
+  <si>
+    <t>reel.jpg</t>
+  </si>
+  <si>
+    <t>Blade-Single-Top-Fullview</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Caliper-Single-Top-Fullview</t>
+  </si>
+  <si>
+    <t>Caliper-Single-Top-Zoomview</t>
+  </si>
+  <si>
+    <t>Caliper</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Device-Multiple-Top-Fullview</t>
+  </si>
+  <si>
+    <t>Cotton-Single-Top-Fullview</t>
+  </si>
+  <si>
+    <t>Cotton-Single-Top-Zoomview</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Label-Multiple-Top-Fullview</t>
+  </si>
+  <si>
+    <t>Bag-Single-Top-Fullview</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Carrier-Single-Top-Fullview</t>
+  </si>
+  <si>
+    <t>Carrier-Multiple-Top-Fullview</t>
+  </si>
+  <si>
+    <t>Reel-Single-Top-Fullview</t>
+  </si>
+  <si>
+    <t>Carrier-Single-Angled-Fullview</t>
+  </si>
+  <si>
+    <t>Reel</t>
+  </si>
+  <si>
+    <t>Device-Single-Angle-Fullview</t>
+  </si>
+  <si>
+    <t>Reel-Single-Angled-Fullview</t>
   </si>
 </sst>
 </file>
@@ -496,13 +577,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D14FA4-9FFF-4ABB-A7F5-DE9BDD01725B}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="17.453125" customWidth="1"/>
-    <col min="3" max="3" width="28.1796875" customWidth="1"/>
-    <col min="4" max="4" width="28.453125" customWidth="1"/>
+    <col min="3" max="3" width="31.81640625" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
     <col min="5" max="5" width="33.453125" customWidth="1"/>
     <col min="6" max="6" width="31.81640625" customWidth="1"/>
     <col min="7" max="7" width="23.36328125" customWidth="1"/>
@@ -531,25 +612,25 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" t="s">
         <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -558,19 +639,19 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -579,19 +660,19 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -600,19 +681,19 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -621,19 +702,19 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -642,19 +723,19 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -663,40 +744,40 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -705,19 +786,19 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -726,229 +807,19 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -959,7 +830,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0060EE3C-7C56-49B0-BD59-6898D4652E99}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" customWidth="1"/>
@@ -979,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -987,7 +858,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -995,7 +866,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1003,7 +874,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1019,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1027,7 +898,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1035,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1043,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1051,86 +922,6 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
     </row>

--- a/backend/exam_data.xlsx
+++ b/backend/exam_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ejcpu\OneDrive\Documents\RDE_EXAM\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D59D076-CF06-45F3-8410-F97EBBF2F2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047DE18E-C9BA-46A3-9CAE-F97498895A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="1590" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{9DB0D4E1-C020-4474-9086-08C7826413CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{9DB0D4E1-C020-4474-9086-08C7826413CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="17">
   <si>
     <t>QuestionNo</t>
   </si>
@@ -72,6 +72,12 @@
     <t>B</t>
   </si>
   <si>
+    <t>STMicroelectronics.jpg</t>
+  </si>
+  <si>
+    <t>SY100.jpg</t>
+  </si>
+  <si>
     <t>Device-Single-Top-Fullview</t>
   </si>
   <si>
@@ -84,94 +90,7 @@
     <t>Label-Single-Top-Fullview</t>
   </si>
   <si>
-    <t>blade.jpg</t>
-  </si>
-  <si>
-    <t>blade3.jpg</t>
-  </si>
-  <si>
-    <t>caliper.jpg</t>
-  </si>
-  <si>
-    <t>carrier.jpg</t>
-  </si>
-  <si>
-    <t>cotton.jpg</t>
-  </si>
-  <si>
-    <t>device7.jpg</t>
-  </si>
-  <si>
-    <t>label.jpg</t>
-  </si>
-  <si>
-    <t>others.jpg</t>
-  </si>
-  <si>
-    <t>reel2.jpg</t>
-  </si>
-  <si>
-    <t>reel.jpg</t>
-  </si>
-  <si>
-    <t>Blade-Single-Top-Fullview</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Caliper-Single-Top-Fullview</t>
-  </si>
-  <si>
-    <t>Caliper-Single-Top-Zoomview</t>
-  </si>
-  <si>
-    <t>Caliper</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Device-Multiple-Top-Fullview</t>
-  </si>
-  <si>
-    <t>Cotton-Single-Top-Fullview</t>
-  </si>
-  <si>
-    <t>Cotton-Single-Top-Zoomview</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Label-Multiple-Top-Fullview</t>
-  </si>
-  <si>
-    <t>Bag-Single-Top-Fullview</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>Carrier-Single-Top-Fullview</t>
-  </si>
-  <si>
-    <t>Carrier-Multiple-Top-Fullview</t>
-  </si>
-  <si>
-    <t>Reel-Single-Top-Fullview</t>
-  </si>
-  <si>
-    <t>Carrier-Single-Angled-Fullview</t>
-  </si>
-  <si>
-    <t>Reel</t>
-  </si>
-  <si>
-    <t>Device-Single-Angle-Fullview</t>
-  </si>
-  <si>
-    <t>Reel-Single-Angled-Fullview</t>
+    <t>Texas.jpg</t>
   </si>
 </sst>
 </file>
@@ -577,13 +496,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D14FA4-9FFF-4ABB-A7F5-DE9BDD01725B}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="17.453125" customWidth="1"/>
-    <col min="3" max="3" width="31.81640625" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="3" max="3" width="28.1796875" customWidth="1"/>
+    <col min="4" max="4" width="28.453125" customWidth="1"/>
     <col min="5" max="5" width="33.453125" customWidth="1"/>
     <col min="6" max="6" width="31.81640625" customWidth="1"/>
     <col min="7" max="7" width="23.36328125" customWidth="1"/>
@@ -612,25 +531,25 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -639,19 +558,19 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -660,19 +579,19 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -681,19 +600,19 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -702,19 +621,19 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -723,19 +642,19 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -744,40 +663,40 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -786,19 +705,19 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -807,19 +726,229 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -830,7 +959,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0060EE3C-7C56-49B0-BD59-6898D4652E99}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" customWidth="1"/>
@@ -850,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -858,7 +987,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -866,7 +995,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -874,7 +1003,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -890,7 +1019,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -898,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -906,7 +1035,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -914,7 +1043,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -922,6 +1051,86 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
